--- a/artfynd/A 19973-2025 artfynd.xlsx
+++ b/artfynd/A 19973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349718</v>
       </c>
       <c r="B2" t="n">
-        <v>91375</v>
+        <v>91380</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128349613</v>
       </c>
       <c r="B3" t="n">
-        <v>79649</v>
+        <v>79650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128349769</v>
       </c>
       <c r="B4" t="n">
-        <v>96075</v>
+        <v>96080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19973-2025 artfynd.xlsx
+++ b/artfynd/A 19973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349718</v>
       </c>
       <c r="B2" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128349613</v>
       </c>
       <c r="B3" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128349769</v>
       </c>
       <c r="B4" t="n">
-        <v>96080</v>
+        <v>96173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19973-2025 artfynd.xlsx
+++ b/artfynd/A 19973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349718</v>
       </c>
       <c r="B2" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128349613</v>
       </c>
       <c r="B3" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128349769</v>
       </c>
       <c r="B4" t="n">
-        <v>96173</v>
+        <v>96185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19973-2025 artfynd.xlsx
+++ b/artfynd/A 19973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349718</v>
       </c>
       <c r="B2" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128349613</v>
       </c>
       <c r="B3" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128349769</v>
       </c>
       <c r="B4" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19973-2025 artfynd.xlsx
+++ b/artfynd/A 19973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349718</v>
       </c>
       <c r="B2" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128349769</v>
       </c>
       <c r="B4" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19973-2025 artfynd.xlsx
+++ b/artfynd/A 19973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349718</v>
       </c>
       <c r="B2" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128349613</v>
       </c>
       <c r="B3" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128349769</v>
       </c>
       <c r="B4" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19973-2025 artfynd.xlsx
+++ b/artfynd/A 19973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349718</v>
       </c>
       <c r="B2" t="n">
-        <v>91514</v>
+        <v>91524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128349613</v>
       </c>
       <c r="B3" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128349769</v>
       </c>
       <c r="B4" t="n">
-        <v>96215</v>
+        <v>96228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19973-2025 artfynd.xlsx
+++ b/artfynd/A 19973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349718</v>
       </c>
       <c r="B2" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128349613</v>
       </c>
       <c r="B3" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128349769</v>
       </c>
       <c r="B4" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19973-2025 artfynd.xlsx
+++ b/artfynd/A 19973-2025 artfynd.xlsx
@@ -675,38 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128349718</v>
+        <v>128349769</v>
       </c>
       <c r="B2" t="n">
-        <v>91528</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607976</v>
+        <v>608005</v>
       </c>
       <c r="R2" t="n">
-        <v>6481313</v>
+        <v>6481342</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128349613</v>
+        <v>128349718</v>
       </c>
       <c r="B3" t="n">
-        <v>79743</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,32 +798,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607852</v>
+        <v>607976</v>
       </c>
       <c r="R3" t="n">
-        <v>6481376</v>
+        <v>6481313</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,45 +892,50 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>William Rosén, Nina Gad Burgman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128349769</v>
+        <v>128349613</v>
       </c>
       <c r="B4" t="n">
-        <v>96232</v>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608005</v>
+        <v>607852</v>
       </c>
       <c r="R4" t="n">
-        <v>6481342</v>
+        <v>6481376</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>William Rosén, Nina Gad Burgman</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 19973-2025 artfynd.xlsx
+++ b/artfynd/A 19973-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128349769</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128349718</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,8 +1028,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128349613</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>